--- a/obras.xlsx
+++ b/obras.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mfournier\Pictures\2026\web-new\manuel_fournier_web_github_pages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E362FCE-E7D7-493D-ABA5-B9E4C3C4880B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F988F3B8-2783-4962-A847-EBF5727DA3B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="58">
   <si>
     <t>Imagen</t>
   </si>
@@ -40,9 +40,6 @@
     <t>Precio</t>
   </si>
   <si>
-    <t>Consultar</t>
-  </si>
-  <si>
     <t>38 x 25 x 20 cm</t>
   </si>
   <si>
@@ -71,6 +68,132 @@
   </si>
   <si>
     <t>Just Before 2</t>
+  </si>
+  <si>
+    <t>Habitats</t>
+  </si>
+  <si>
+    <t>Alquiler Vacacional</t>
+  </si>
+  <si>
+    <t>110 x 40 x 40 cm</t>
+  </si>
+  <si>
+    <t>Collage sobre lienzo</t>
+  </si>
+  <si>
+    <t>60 x 40 cm</t>
+  </si>
+  <si>
+    <t>Almacen</t>
+  </si>
+  <si>
+    <t>1almacen.jpg</t>
+  </si>
+  <si>
+    <t>1Verano.jpg</t>
+  </si>
+  <si>
+    <t>1grande.png</t>
+  </si>
+  <si>
+    <t>350 EUR</t>
+  </si>
+  <si>
+    <t>450 EUR</t>
+  </si>
+  <si>
+    <t>Gentrificacion</t>
+  </si>
+  <si>
+    <t>Escultura. Madera, resina policromada</t>
+  </si>
+  <si>
+    <t>granero.jpg</t>
+  </si>
+  <si>
+    <t>Granero</t>
+  </si>
+  <si>
+    <t>40 x 60 cm</t>
+  </si>
+  <si>
+    <t>250 EUR</t>
+  </si>
+  <si>
+    <t>Habitats 1</t>
+  </si>
+  <si>
+    <t>Habitats 2</t>
+  </si>
+  <si>
+    <t>Habitats 3</t>
+  </si>
+  <si>
+    <t>Habitats 4</t>
+  </si>
+  <si>
+    <t>Habitats 5</t>
+  </si>
+  <si>
+    <t>Habitats 7</t>
+  </si>
+  <si>
+    <t>Habitats 6</t>
+  </si>
+  <si>
+    <t>20250823_125723.jpg</t>
+  </si>
+  <si>
+    <t>20250823_125757.jpg</t>
+  </si>
+  <si>
+    <t>20250823_125842.jpg</t>
+  </si>
+  <si>
+    <t>20250823_125910.jpg</t>
+  </si>
+  <si>
+    <t>20250823_125951.jpg</t>
+  </si>
+  <si>
+    <t>20250823_130021.jpg</t>
+  </si>
+  <si>
+    <t>60 x 25 cm</t>
+  </si>
+  <si>
+    <t>Vendido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Escultura </t>
+  </si>
+  <si>
+    <t>20240724_191954.jpg</t>
+  </si>
+  <si>
+    <t>20240724_191804.jpg</t>
+  </si>
+  <si>
+    <t>Habitats 8</t>
+  </si>
+  <si>
+    <t>Escultura</t>
+  </si>
+  <si>
+    <t>esfera.jpg</t>
+  </si>
+  <si>
+    <t>Esfera</t>
+  </si>
+  <si>
+    <t>45 x 45 x 45 cm</t>
+  </si>
+  <si>
+    <t>Escultura madera policromada. Resina</t>
+  </si>
+  <si>
+    <t>550 EUR</t>
   </si>
 </sst>
 </file>
@@ -143,8 +266,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaObras" displayName="TablaObras" ref="A1:F3">
-  <autoFilter ref="A1:F3" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaObras" displayName="TablaObras" ref="A1:F16">
+  <autoFilter ref="A1:F16" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Imagen"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Serie"/>
@@ -442,7 +565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -475,42 +598,296 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="F2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>8</v>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/obras.xlsx
+++ b/obras.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mfournier\Pictures\2026\web-new\manuel_fournier_web_github_pages\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F988F3B8-2783-4962-A847-EBF5727DA3B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C9D8784-363A-45E6-A910-3F06034550E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -613,7 +613,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -633,7 +633,7 @@
         <v>13</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">

--- a/obras.xlsx
+++ b/obras.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mfournier\Pictures\2026\web-new\manuel_fournier_web_github_pages\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mfournier\Pictures\2026\web-new\manuel-fournier-web-final-completa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C9D8784-363A-45E6-A910-3F06034550E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D266F53-0AB7-40AC-AEBE-427FE4D403EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="95">
   <si>
     <t>Imagen</t>
   </si>
@@ -166,9 +166,6 @@
     <t>Vendido</t>
   </si>
   <si>
-    <t xml:space="preserve">Escultura </t>
-  </si>
-  <si>
     <t>20240724_191954.jpg</t>
   </si>
   <si>
@@ -194,13 +191,127 @@
   </si>
   <si>
     <t>550 EUR</t>
+  </si>
+  <si>
+    <t>pixelcut-export_Nero AI_Face_Nero AI_Face.jpeg</t>
+  </si>
+  <si>
+    <t>Baloons</t>
+  </si>
+  <si>
+    <t>20240612_124729.jpg</t>
+  </si>
+  <si>
+    <t>OBRA 2 - Manuel Fournier.jpg</t>
+  </si>
+  <si>
+    <t>20240526_131248.jpg</t>
+  </si>
+  <si>
+    <t>20240608_134747.jpg</t>
+  </si>
+  <si>
+    <t>300 EUR</t>
+  </si>
+  <si>
+    <t>47 x 15 x 15</t>
+  </si>
+  <si>
+    <t>Habitats3-MFournier.jpg</t>
+  </si>
+  <si>
+    <t>Habitats 10</t>
+  </si>
+  <si>
+    <t>50 x 25 cm</t>
+  </si>
+  <si>
+    <t>Habitats 11</t>
+  </si>
+  <si>
+    <t>Escultura de pared</t>
+  </si>
+  <si>
+    <t>Habitats5-MFournier.jpg</t>
+  </si>
+  <si>
+    <t>Baloons 1</t>
+  </si>
+  <si>
+    <t>Baloons 2</t>
+  </si>
+  <si>
+    <t>Baloons 3</t>
+  </si>
+  <si>
+    <t>Baloons 4</t>
+  </si>
+  <si>
+    <t>Baloons 5</t>
+  </si>
+  <si>
+    <t>ave-Fpurnier.jpg</t>
+  </si>
+  <si>
+    <t>Mediterraneo-Fournier.jpg</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Ave</t>
+  </si>
+  <si>
+    <t>Mediterráneo</t>
+  </si>
+  <si>
+    <t>Escultura. Cubiertos reciclados. Madera</t>
+  </si>
+  <si>
+    <t>Escultura. Botellas recicladas y resina</t>
+  </si>
+  <si>
+    <t>110 x 18 x 22 cm</t>
+  </si>
+  <si>
+    <t>50 x 30 x 15 cm</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>the-forbidden-fruit-eva.jpg</t>
+  </si>
+  <si>
+    <t>Eva - La fruta prohibida</t>
+  </si>
+  <si>
+    <t>40 x 25 x 25 cm</t>
+  </si>
+  <si>
+    <t>Escultura resina policromada</t>
+  </si>
+  <si>
+    <t>otra.jpg</t>
+  </si>
+  <si>
+    <t>Habitats a</t>
+  </si>
+  <si>
+    <t>Habitats b</t>
+  </si>
+  <si>
+    <t>Collages madera, papel, textil y oxidacion</t>
+  </si>
+  <si>
+    <t>otra2.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -214,8 +325,14 @@
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -227,8 +344,14 @@
         <fgColor rgb="FF1F1F1F"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -236,11 +359,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -248,6 +382,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -266,8 +405,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaObras" displayName="TablaObras" ref="A1:F16">
-  <autoFilter ref="A1:F16" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TablaObras" displayName="TablaObras" ref="A1:F24">
+  <autoFilter ref="A1:F24" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Imagen"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Serie"/>
@@ -565,7 +704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -658,22 +797,22 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
         <v>53</v>
       </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>54</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>55</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>56</v>
-      </c>
-      <c r="F5" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -858,7 +997,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B15" t="s">
         <v>16</v>
@@ -866,8 +1005,11 @@
       <c r="C15" t="s">
         <v>38</v>
       </c>
+      <c r="D15" t="s">
+        <v>67</v>
+      </c>
       <c r="E15" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="F15" t="s">
         <v>47</v>
@@ -875,19 +1017,250 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B16" t="s">
         <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>50</v>
+      </c>
+      <c r="D16" t="s">
+        <v>67</v>
       </c>
       <c r="E16" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="F16" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" t="s">
+        <v>51</v>
+      </c>
+      <c r="F19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" t="s">
+        <v>51</v>
+      </c>
+      <c r="F20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" t="s">
+        <v>51</v>
+      </c>
+      <c r="F21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E22" t="s">
+        <v>69</v>
+      </c>
+      <c r="F22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D23" t="s">
+        <v>67</v>
+      </c>
+      <c r="E23" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>76</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" t="s">
+        <v>79</v>
+      </c>
+      <c r="D24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" t="s">
+        <v>81</v>
+      </c>
+      <c r="F24" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>77</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" t="s">
+        <v>80</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E25" t="s">
+        <v>82</v>
+      </c>
+      <c r="F25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" t="s">
+        <v>85</v>
+      </c>
+      <c r="C26" t="s">
+        <v>87</v>
+      </c>
+      <c r="D26" t="s">
+        <v>88</v>
+      </c>
+      <c r="E26" t="s">
+        <v>89</v>
+      </c>
+      <c r="F26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>90</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="s">
+        <v>91</v>
+      </c>
+      <c r="D27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" t="s">
+        <v>93</v>
+      </c>
+      <c r="F27" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>94</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" t="s">
+        <v>93</v>
+      </c>
+      <c r="F28" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/obras.xlsx
+++ b/obras.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mfournier\Pictures\2026\web-new\manuel-fournier-web-final-completa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D66FBE8-9C2D-4008-8283-C201BD3651BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{499B1A52-2F28-4839-BCD8-8E80F709EACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Obras" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Obras!$A$1:$F$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Obras!$A$1:$F$25</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="80">
   <si>
     <t>Imagen</t>
   </si>
@@ -154,12 +154,6 @@
     <t>Habitats 2</t>
   </si>
   <si>
-    <t>20250823_125842.jpg</t>
-  </si>
-  <si>
-    <t>Habitats 3</t>
-  </si>
-  <si>
     <t>20250823_125910.jpg</t>
   </si>
   <si>
@@ -268,7 +262,7 @@
     <t>designer.jpg</t>
   </si>
   <si>
-    <t>Habitats-1b</t>
+    <t>Habitats-3</t>
   </si>
 </sst>
 </file>
@@ -290,7 +284,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -300,6 +294,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -315,12 +315,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -625,7 +628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -697,7 +700,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -717,7 +720,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -737,7 +740,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -757,7 +760,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -777,7 +780,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -818,13 +821,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>39</v>
@@ -917,7 +920,7 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>49</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -927,33 +930,33 @@
         <v>50</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="F16" s="2" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -961,39 +964,37 @@
         <v>56</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -1001,17 +1002,17 @@
         <v>64</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>65</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -1019,17 +1020,17 @@
         <v>66</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -1037,17 +1038,17 @@
         <v>68</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -1055,17 +1056,19 @@
         <v>70</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D22" s="2"/>
+      <c r="D22" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="E22" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -1079,13 +1082,13 @@
         <v>73</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -1093,59 +1096,39 @@
         <v>74</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>53</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="D24" s="2"/>
       <c r="E24" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F26" s="2" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F26" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F25" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>